--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_368_R37.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_368_R37.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.1382</v>
+        <v>6.2803</v>
       </c>
       <c r="E2" t="n">
-        <v>7.0736</v>
+        <v>6.7197</v>
       </c>
       <c r="F2" t="n">
-        <v>0.06469999999999999</v>
+        <v>-0.4394</v>
       </c>
       <c r="G2" t="n">
         <v>1.7819</v>
@@ -610,13 +610,13 @@
         <v>1.8556</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3949</v>
+        <v>-0.463</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1019</v>
+        <v>-0.4558</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4969</v>
+        <v>-0.0072</v>
       </c>
       <c r="V2" t="n">
         <v>3.1058</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.9215</v>
+        <v>4.4434</v>
       </c>
       <c r="E3" t="n">
-        <v>6.8678</v>
+        <v>7.2217</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.9463</v>
+        <v>-2.7783</v>
       </c>
       <c r="G3" t="n">
         <v>3.7422</v>
@@ -688,13 +688,13 @@
         <v>1.6237</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.8929</v>
+        <v>-1.3711</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.8962</v>
+        <v>-0.5423</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.9968</v>
+        <v>-0.8287</v>
       </c>
       <c r="V3" t="n">
         <v>1.6083</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.9245</v>
+        <v>2.5034</v>
       </c>
       <c r="E4" t="n">
-        <v>4.3395</v>
+        <v>3.9856</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.4149</v>
+        <v>-1.4822</v>
       </c>
       <c r="G4" t="n">
         <v>1.8843</v>
@@ -766,13 +766,13 @@
         <v>1.8556</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3444</v>
+        <v>-0.0767</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8338</v>
+        <v>0.4799</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.4894</v>
+        <v>-0.5566</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.7492</v>
+        <v>-0.3274</v>
       </c>
       <c r="E5" t="n">
-        <v>1.7268</v>
+        <v>2.3166</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.476</v>
+        <v>-2.644</v>
       </c>
       <c r="G5" t="n">
         <v>0.8525</v>
@@ -844,13 +844,13 @@
         <v>0.4639</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1946</v>
+        <v>0.2271</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5149</v>
+        <v>0.07489999999999999</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3203</v>
+        <v>0.1522</v>
       </c>
       <c r="V5" t="n">
         <v>1.6083</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.2074</v>
+        <v>-1.2746</v>
       </c>
       <c r="E6" t="n">
         <v>-1.0315</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.1759</v>
+        <v>-0.2432</v>
       </c>
       <c r="G6" t="n">
         <v>-1.312</v>
@@ -922,13 +922,13 @@
         <v>0.232</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1274</v>
+        <v>-0.1946</v>
       </c>
       <c r="T6" t="n">
         <v>-0.2987</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1713</v>
+        <v>0.1041</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.5877</v>
+        <v>-1.8915</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5669</v>
+        <v>0.0951</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.1546</v>
+        <v>-1.9866</v>
       </c>
       <c r="G7" t="n">
         <v>-2.6509</v>
@@ -1000,13 +1000,13 @@
         <v>1.6237</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4187</v>
+        <v>-0.7224</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1221</v>
+        <v>-0.3497</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.5407999999999999</v>
+        <v>-0.3727</v>
       </c>
       <c r="V7" t="n">
         <v>-0.1418</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Z. SELJAAS</t>
+          <t>D. LIGHTY</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.1962</v>
+        <v>-2.8704</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.4291</v>
+        <v>-1.4418</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.7671</v>
+        <v>-1.4286</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.7624</v>
+        <v>-2.6004</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.066</v>
+        <v>-1.774</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.6964</v>
+        <v>-0.8264</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.4687</v>
+        <v>-1.1238</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.7191</v>
+        <v>-0.6687</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.7495000000000001</v>
+        <v>-0.4551</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.2938</v>
+        <v>-1.4766</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3469</v>
+        <v>-1.1053</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.9469</v>
+        <v>-0.3713</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.4639</v>
+        <v>1.1598</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.6959</v>
+        <v>1.1598</v>
       </c>
       <c r="S8" t="n">
-        <v>1.2441</v>
+        <v>-0.4993</v>
       </c>
       <c r="T8" t="n">
-        <v>1.1993</v>
+        <v>-0.4597</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0448</v>
+        <v>-0.0395</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.214</v>
+        <v>-0.9304</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.214</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. LIGHTY</t>
+          <t>Z. SELJAAS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.3587</v>
+        <v>-3.8367</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.7956</v>
+        <v>-2.1368</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.563</v>
+        <v>-1.6999</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.6004</v>
+        <v>-2.7624</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.774</v>
+        <v>-1.066</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.8264</v>
+        <v>-1.6964</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.1238</v>
+        <v>-1.4687</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.6687</v>
+        <v>-0.7191</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.4551</v>
+        <v>-0.7495000000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.4766</v>
+        <v>-1.2938</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.1053</v>
+        <v>-0.3469</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.3713</v>
+        <v>-0.9469</v>
       </c>
       <c r="P9" t="n">
-        <v>1.1598</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1598</v>
+        <v>0.6959</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.9875</v>
+        <v>0.6036</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8136</v>
+        <v>0.4916</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.174</v>
+        <v>0.112</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.9304</v>
+        <v>-1.214</v>
       </c>
       <c r="W9" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.0722</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.4981</v>
+        <v>-4.3637</v>
       </c>
       <c r="E10" t="n">
         <v>-2.2501</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.248</v>
+        <v>-2.1136</v>
       </c>
       <c r="G10" t="n">
         <v>-1.0597</v>
@@ -1234,13 +1234,13 @@
         <v>0.4639</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.905</v>
+        <v>-0.7705</v>
       </c>
       <c r="T10" t="n">
         <v>-0.5975</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3075</v>
+        <v>-0.1731</v>
       </c>
       <c r="V10" t="n">
         <v>-0.6778999999999999</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.4993</v>
+        <v>-4.4486</v>
       </c>
       <c r="E11" t="n">
-        <v>0.6491</v>
+        <v>0.767</v>
       </c>
       <c r="F11" t="n">
-        <v>-5.1484</v>
+        <v>-5.2156</v>
       </c>
       <c r="G11" t="n">
         <v>-3.4082</v>
@@ -1312,13 +1312,13 @@
         <v>0.9278</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2689</v>
+        <v>-0.2181</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0395</v>
+        <v>0.1575</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3084</v>
+        <v>-0.3756</v>
       </c>
       <c r="V11" t="n">
         <v>-1.7501</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.4084</v>
+        <v>-4.7349</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.3893</v>
+        <v>-2.9175</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.0191</v>
+        <v>-1.8174</v>
       </c>
       <c r="G12" t="n">
         <v>-4.2287</v>
@@ -1390,13 +1390,13 @@
         <v>0.6959</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.6282</v>
+        <v>0.0452</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5228</v>
+        <v>-0.051</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1054</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="V12" t="n">
         <v>1.0722</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-10.5208</v>
+        <v>-10.5207</v>
       </c>
       <c r="E13" t="n">
-        <v>11.3281</v>
+        <v>11.328</v>
       </c>
       <c r="F13" t="n">
-        <v>-21.8486</v>
+        <v>-21.8488</v>
       </c>
       <c r="G13" t="n">
         <v>-9.761400000000002</v>
@@ -1471,10 +1471,10 @@
         <v>-3.4398</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.5509</v>
+        <v>-1.5508</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.889</v>
+        <v>-1.8889</v>
       </c>
       <c r="V13" t="n">
         <v>2.6804</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.9727</v>
+        <v>4.0456</v>
       </c>
       <c r="E15" t="n">
-        <v>4.7279</v>
+        <v>4.6099</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.7552</v>
+        <v>-0.5643</v>
       </c>
       <c r="G15" t="n">
         <v>2.8264</v>
@@ -1624,13 +1624,13 @@
         <v>0.9278</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.0523</v>
+        <v>0.0206</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.0351</v>
+        <v>-0.1531</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0171</v>
+        <v>0.1737</v>
       </c>
       <c r="V15" t="n">
         <v>2.8223</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.1906</v>
+        <v>2.5856</v>
       </c>
       <c r="E16" t="n">
         <v>1.9525</v>
       </c>
       <c r="F16" t="n">
-        <v>1.2381</v>
+        <v>0.6332</v>
       </c>
       <c r="G16" t="n">
         <v>-0.7475000000000001</v>
@@ -1702,13 +1702,13 @@
         <v>1.3917</v>
       </c>
       <c r="S16" t="n">
-        <v>2.0102</v>
+        <v>1.4053</v>
       </c>
       <c r="T16" t="n">
         <v>0.4876</v>
       </c>
       <c r="U16" t="n">
-        <v>1.5226</v>
+        <v>0.9177</v>
       </c>
       <c r="V16" t="n">
         <v>0.5361</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.442</v>
+        <v>2.1897</v>
       </c>
       <c r="E17" t="n">
-        <v>1.7971</v>
+        <v>1.6792</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6449</v>
+        <v>0.5105</v>
       </c>
       <c r="G17" t="n">
         <v>1.7432</v>
@@ -1780,13 +1780,13 @@
         <v>1.6237</v>
       </c>
       <c r="S17" t="n">
-        <v>0.9129</v>
+        <v>0.6605</v>
       </c>
       <c r="T17" t="n">
-        <v>0.4129</v>
+        <v>0.295</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4999</v>
+        <v>0.3655</v>
       </c>
       <c r="V17" t="n">
         <v>-0.6778999999999999</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.2757</v>
+        <v>1.5052</v>
       </c>
       <c r="E18" t="n">
-        <v>6.2769</v>
+        <v>4.9794</v>
       </c>
       <c r="F18" t="n">
-        <v>-4.0012</v>
+        <v>-3.4742</v>
       </c>
       <c r="G18" t="n">
         <v>1.7291</v>
@@ -1858,13 +1858,13 @@
         <v>0.9278</v>
       </c>
       <c r="S18" t="n">
-        <v>0.923</v>
+        <v>0.1524</v>
       </c>
       <c r="T18" t="n">
-        <v>1.6201</v>
+        <v>0.3227</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.6972</v>
+        <v>-0.1702</v>
       </c>
       <c r="V18" t="n">
         <v>-1.0722</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. BOLOMBOY</t>
+          <t>S. MILJENOVIC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.1177</v>
+        <v>1.1733</v>
       </c>
       <c r="E19" t="n">
-        <v>2.7737</v>
+        <v>-0.167</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.656</v>
+        <v>1.3404</v>
       </c>
       <c r="G19" t="n">
-        <v>0.2127</v>
+        <v>1.14</v>
       </c>
       <c r="H19" t="n">
-        <v>0.7648</v>
+        <v>0.3938</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.5521</v>
+        <v>0.7461</v>
       </c>
       <c r="J19" t="n">
-        <v>2.2782</v>
+        <v>0.6897</v>
       </c>
       <c r="K19" t="n">
-        <v>0.6722</v>
+        <v>0.1008</v>
       </c>
       <c r="L19" t="n">
-        <v>1.606</v>
+        <v>0.5889</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.0655</v>
+        <v>0.4502</v>
       </c>
       <c r="N19" t="n">
-        <v>0.0926</v>
+        <v>0.293</v>
       </c>
       <c r="O19" t="n">
-        <v>-2.1581</v>
+        <v>0.1573</v>
       </c>
       <c r="P19" t="n">
-        <v>0.6959</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R19" t="n">
         <v>0.6959</v>
       </c>
       <c r="S19" t="n">
-        <v>0.2091</v>
+        <v>0.4973</v>
       </c>
       <c r="T19" t="n">
-        <v>0.4955</v>
+        <v>0.1612</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2864</v>
+        <v>0.3361</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S. MILJENOVIC</t>
+          <t>J. BOLOMBOY</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.7358</v>
+        <v>0.8653</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.4029</v>
+        <v>2.6558</v>
       </c>
       <c r="F20" t="n">
-        <v>1.1387</v>
+        <v>-1.7905</v>
       </c>
       <c r="G20" t="n">
-        <v>1.14</v>
+        <v>0.2127</v>
       </c>
       <c r="H20" t="n">
-        <v>0.3938</v>
+        <v>0.7648</v>
       </c>
       <c r="I20" t="n">
-        <v>0.7461</v>
+        <v>-0.5521</v>
       </c>
       <c r="J20" t="n">
-        <v>0.6897</v>
+        <v>2.2782</v>
       </c>
       <c r="K20" t="n">
-        <v>0.1008</v>
+        <v>0.6722</v>
       </c>
       <c r="L20" t="n">
-        <v>0.5889</v>
+        <v>1.606</v>
       </c>
       <c r="M20" t="n">
-        <v>0.4502</v>
+        <v>-2.0655</v>
       </c>
       <c r="N20" t="n">
-        <v>0.293</v>
+        <v>0.0926</v>
       </c>
       <c r="O20" t="n">
-        <v>0.1573</v>
+        <v>-2.1581</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.4639</v>
+        <v>0.6959</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
         <v>0.6959</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0597</v>
+        <v>-0.0433</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0747</v>
+        <v>0.3776</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1344</v>
+        <v>-0.4208</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.9913999999999999</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="E21" t="n">
-        <v>0.3588</v>
+        <v>1.0665</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.3502</v>
+        <v>-0.9805</v>
       </c>
       <c r="G21" t="n">
         <v>0.5198</v>
@@ -2092,13 +2092,13 @@
         <v>1.6237</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3668</v>
+        <v>0.7106</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1415</v>
+        <v>0.5663</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2254</v>
+        <v>0.1443</v>
       </c>
       <c r="V21" t="n">
         <v>-1.6083</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.6539</v>
+        <v>-1.4795</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.5163</v>
+        <v>-1.3983</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.1376</v>
+        <v>-0.08119999999999999</v>
       </c>
       <c r="G22" t="n">
         <v>-0.893</v>
@@ -2170,13 +2170,13 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0.1489</v>
+        <v>0.3233</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3734</v>
+        <v>-0.2555</v>
       </c>
       <c r="U22" t="n">
-        <v>0.5223</v>
+        <v>0.5788</v>
       </c>
       <c r="V22" t="n">
         <v>-0.6778999999999999</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>O. DOBRIC</t>
+          <t>C. MILLER-MCINTYRE</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.6393</v>
+        <v>-2.4228</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.3592</v>
+        <v>1.4953</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.2801</v>
+        <v>-3.9181</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.8907</v>
+        <v>0.6022999999999999</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.9639</v>
+        <v>2.7538</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.9268</v>
+        <v>-2.1515</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.6791</v>
+        <v>3.9332</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.7527</v>
+        <v>3.3981</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0736</v>
+        <v>0.5351</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.2116</v>
+        <v>-3.3309</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.2112</v>
+        <v>-0.6443</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.0004</v>
+        <v>-2.6866</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>-2.0876</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.232</v>
+        <v>-3.7112</v>
       </c>
       <c r="R23" t="n">
-        <v>0.232</v>
+        <v>1.6237</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.7486</v>
+        <v>0.1346</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4481</v>
+        <v>0.0593</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3005</v>
+        <v>0.07530000000000001</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.214</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-2.2862</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>C. MILLER-MCINTYRE</t>
+          <t>O. DOBRIC</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.8496</v>
+        <v>-2.5885</v>
       </c>
       <c r="E24" t="n">
-        <v>1.2594</v>
+        <v>-1.2412</v>
       </c>
       <c r="F24" t="n">
-        <v>-4.109</v>
+        <v>-1.3473</v>
       </c>
       <c r="G24" t="n">
-        <v>0.6022999999999999</v>
+        <v>-1.8907</v>
       </c>
       <c r="H24" t="n">
-        <v>2.7538</v>
+        <v>-0.9639</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.1515</v>
+        <v>-0.9268</v>
       </c>
       <c r="J24" t="n">
-        <v>3.9332</v>
+        <v>-0.6791</v>
       </c>
       <c r="K24" t="n">
-        <v>3.3981</v>
+        <v>-0.7527</v>
       </c>
       <c r="L24" t="n">
-        <v>0.5351</v>
+        <v>0.0736</v>
       </c>
       <c r="M24" t="n">
-        <v>-3.3309</v>
+        <v>-1.2116</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.6443</v>
+        <v>-0.2112</v>
       </c>
       <c r="O24" t="n">
-        <v>-2.6866</v>
+        <v>-1.0004</v>
       </c>
       <c r="P24" t="n">
-        <v>-2.0876</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>-3.7112</v>
+        <v>-0.232</v>
       </c>
       <c r="R24" t="n">
-        <v>1.6237</v>
+        <v>0.232</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.2921</v>
+        <v>-0.6978</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.1766</v>
+        <v>-0.3301</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1155</v>
+        <v>-0.3677</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.214</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-2.2862</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.7308</v>
+        <v>-3.304</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.2216</v>
+        <v>-2.9857</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.5091</v>
+        <v>-0.3182</v>
       </c>
       <c r="G25" t="n">
         <v>-2.8382</v>
@@ -2404,13 +2404,13 @@
         <v>0.4639</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.2842</v>
+        <v>0.1426</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.5228</v>
+        <v>-0.2869</v>
       </c>
       <c r="U25" t="n">
-        <v>0.2385</v>
+        <v>0.4294</v>
       </c>
       <c r="V25" t="n">
         <v>-1.0722</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>10.5207</v>
+        <v>11.3071</v>
       </c>
       <c r="E26" t="n">
-        <v>21.707</v>
+        <v>21.7071</v>
       </c>
       <c r="F26" t="n">
-        <v>-11.1862</v>
+        <v>-10.3997</v>
       </c>
       <c r="G26" t="n">
         <v>9.761699999999996</v>
@@ -2482,13 +2482,13 @@
         <v>11.5978</v>
       </c>
       <c r="S26" t="n">
-        <v>3.439700000000001</v>
+        <v>4.225999999999999</v>
       </c>
       <c r="T26" t="n">
-        <v>1.888799999999999</v>
+        <v>1.889</v>
       </c>
       <c r="U26" t="n">
-        <v>1.5506</v>
+        <v>2.3371</v>
       </c>
       <c r="V26" t="n">
         <v>-2.6805</v>
